--- a/artfynd/S 3556-2023 artfynd.xlsx
+++ b/artfynd/S 3556-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AZ78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -793,6 +798,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527706</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -919,6 +929,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975576</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1040,6 +1055,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1166,6 +1186,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975969</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1287,6 +1312,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527697</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1408,6 +1438,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527704</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1529,6 +1564,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527712</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1655,6 +1695,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975799</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1781,6 +1826,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975801</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1902,6 +1952,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2028,6 +2083,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102976983</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2149,6 +2209,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527694</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2270,6 +2335,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527698</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2391,6 +2461,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527701</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2512,6 +2587,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527710</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2638,6 +2718,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974367</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2764,6 +2849,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974369</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2890,6 +2980,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974371</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3011,6 +3106,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527693</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3132,6 +3232,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527711</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3258,6 +3363,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102978846</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3379,6 +3489,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527699</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3495,6 +3610,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/457494</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3607,6 +3727,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59387761</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3718,6 +3843,11 @@
           <t>Smålands flora (1978-2007)</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75026181</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3835,6 +3965,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96157296</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3956,6 +4091,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69535842</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4082,6 +4222,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975654</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4203,6 +4348,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537616</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4324,6 +4474,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537618</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4445,6 +4600,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537622</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4566,6 +4726,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69537623</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4692,6 +4857,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975944</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4818,6 +4988,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975945</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4944,6 +5119,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102978952</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5065,6 +5245,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525956</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5186,6 +5371,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525957</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5307,6 +5497,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525958</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5428,6 +5623,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525959</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5549,6 +5749,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525960</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5670,6 +5875,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525961</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5791,6 +6001,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69525963</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5917,6 +6132,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975603</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6043,6 +6263,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975607</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6169,6 +6394,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102978741</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -6295,6 +6525,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975679</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -6421,6 +6656,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975682</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6547,6 +6787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102977034</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6673,6 +6918,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102977035</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6799,6 +7049,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102978772</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6925,6 +7180,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102978773</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7046,6 +7306,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527695</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7167,6 +7432,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527696</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -7288,6 +7558,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527700</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -7409,6 +7684,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527707</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -7530,6 +7810,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527709</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7651,6 +7936,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527714</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7772,6 +8062,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527703</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7893,6 +8188,11 @@
           <t>Trädinventeringen i Kalmar län</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69527716</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8019,6 +8319,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975496</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -8145,6 +8450,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102975497</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -8271,6 +8581,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/102974394</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -8397,6 +8712,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63201169</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -8523,6 +8843,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63193304</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -8649,6 +8974,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63202106</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8775,6 +9105,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63189671</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8901,6 +9236,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63225976</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9027,6 +9367,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/63228881</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -9129,6 +9474,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3534299</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -9231,6 +9581,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93917828</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -9341,6 +9696,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103062541</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -9454,6 +9814,11 @@
       <c r="AY73" t="inlineStr">
         <is>
           <t>Trädportalen</t>
+        </is>
+      </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103063838</t>
         </is>
       </c>
     </row>
@@ -9558,6 +9923,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93917839</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -9665,6 +10035,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5192275</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9774,6 +10149,11 @@
       <c r="AY76" t="inlineStr">
         <is>
           <t>Smålands flora (1978-2007)</t>
+        </is>
+      </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/74700792</t>
         </is>
       </c>
     </row>
@@ -9878,6 +10258,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93917842</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9980,8 +10365,92 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5779092</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>